--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260701.xlsx
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>14,827,000</t>
+          <t>16,986,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>16,986,000</t>
+          <t>14,827,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>11,807,000</t>
+          <t>3,944,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>3,944,000</t>
+          <t>11,807,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>新產</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,350,000</t>
+          <t>5,564,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>新產</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>5,564,000</t>
+          <t>7,350,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
